--- a/flight_schedule.xlsx
+++ b/flight_schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/aadb9d128a4cfa1d/Documenten/python/Operations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="8_{7E816CCE-281B-4C38-AAF5-984D86C15AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E9C6CA7-FDA2-4A36-8E89-6F5DD7ED243E}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="8_{7E816CCE-281B-4C38-AAF5-984D86C15AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A97C09A5-60C3-4863-9B9F-155C6155F49E}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{A1FE08AC-126B-4F31-942F-8CEC59BBF880}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A1FE08AC-126B-4F31-942F-8CEC59BBF880}"/>
   </bookViews>
   <sheets>
     <sheet name="A" sheetId="2" r:id="rId1"/>
@@ -547,6 +547,7 @@
         <v>5</v>
       </c>
       <c r="C3">
+        <f t="shared" ref="C3:C11" si="0">C2+90</f>
         <v>90</v>
       </c>
       <c r="D3" t="s">
@@ -561,7 +562,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C11" si="0">C3+90</f>
+        <f t="shared" si="0"/>
         <v>180</v>
       </c>
       <c r="D4" t="s">
